--- a/data/trans_orig/IP16B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Estudios-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51426</t>
+          <t>51083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56397</t>
+          <t>55982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60651</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109445</t>
+          <t>109361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114546</t>
+          <t>114682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>445602</t>
+          <t>445754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>452570</t>
+          <t>452648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>491927</t>
+          <t>492282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>501751</t>
+          <t>501668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>940090</t>
+          <t>939729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952704</t>
+          <t>953030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138096</t>
+          <t>137849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145257</t>
+          <t>145362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177023</t>
+          <t>176735</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181336</t>
+          <t>181372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317321</t>
+          <t>317650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325632</t>
+          <t>325943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>640485</t>
+          <t>640480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>650457</t>
+          <t>650547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>730668</t>
+          <t>730188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>741879</t>
+          <t>741701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1374596</t>
+          <t>1375671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1390230</t>
+          <t>1389967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54303</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50720</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55612</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>53630</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51083</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54233</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45874</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>43544</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46399</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59301</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>55982</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60654</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112931</t>
+          <t>100177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109361</t>
+          <t>96698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114682</t>
+          <t>101731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3150</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5061</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55922</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55922</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55922</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54233</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54233</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54233</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115276</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115276</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115276</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>458588</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>453600</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>462009</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>449997</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>445754</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>452648</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>497939</t>
+          <t>422992</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>492282</t>
+          <t>419450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>501668</t>
+          <t>425158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>947937</t>
+          <t>881580</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>939729</t>
+          <t>874907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>953030</t>
+          <t>885538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13189</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2261</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9155</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466789</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466789</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466789</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>636</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>454909</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>454909</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>454909</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>507367</t>
+          <t>427010</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>507367</t>
+          <t>427010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>507367</t>
+          <t>427010</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>962277</t>
+          <t>893799</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>962277</t>
+          <t>893799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>962277</t>
+          <t>893799</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>166077</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>163927</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>167293</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>142609</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>137849</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>179941</t>
+          <t>143056</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176735</t>
+          <t>137916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181372</t>
+          <t>145622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>322551</t>
+          <t>309133</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317650</t>
+          <t>303827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325943</t>
+          <t>312090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4864</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9624</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147473</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147473</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147473</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182174</t>
+          <t>147880</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182174</t>
+          <t>147880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182174</t>
+          <t>147880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329647</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329647</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329647</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>672766</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>683176</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>646237</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>640480</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>650547</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>737181</t>
+          <t>611922</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>730188</t>
+          <t>605820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>741701</t>
+          <t>615501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1383417</t>
+          <t>1290890</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1375671</t>
+          <t>1283099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1389967</t>
+          <t>1297147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17814</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10378</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6068</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16135</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>931</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>656615</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>656615</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>656615</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621289</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1407199</t>
+          <t>1311869</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1407199</t>
+          <t>1311869</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1407199</t>
+          <t>1311869</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
